--- a/results/manual/Azerbaijan/reviewers/reviewer_A.xlsx
+++ b/results/manual/Azerbaijan/reviewers/reviewer_A.xlsx
@@ -152,34 +152,34 @@
     <t>halva | azerbaijani rice | lamb</t>
   </si>
   <si>
+    <t>Incorrect</t>
+  </si>
+  <si>
+    <t>Clearly wrong or incompatible</t>
+  </si>
+  <si>
+    <t>Jo-sp-01</t>
+  </si>
+  <si>
+    <t>Sport</t>
+  </si>
+  <si>
+    <t>Azərbaycanda ikinci ən populyar idman növü hansıdır?</t>
+  </si>
+  <si>
+    <t>What is the second most popular sport in Azerbaijan?</t>
+  </si>
+  <si>
+    <t>Futbol</t>
+  </si>
+  <si>
+    <t>basketbol | şahmat | güləş | voleybol</t>
+  </si>
+  <si>
+    <t>basketball | chess | wrestling | volleyball</t>
+  </si>
+  <si>
     <t>Uncertain</t>
-  </si>
-  <si>
-    <t>Incorrect</t>
-  </si>
-  <si>
-    <t>Clearly wrong or incompatible</t>
-  </si>
-  <si>
-    <t>Jo-sp-01</t>
-  </si>
-  <si>
-    <t>Sport</t>
-  </si>
-  <si>
-    <t>Azərbaycanda ikinci ən populyar idman növü hansıdır?</t>
-  </si>
-  <si>
-    <t>What is the second most popular sport in Azerbaijan?</t>
-  </si>
-  <si>
-    <t>Futbol</t>
-  </si>
-  <si>
-    <t>basketbol | şahmat | güləş | voleybol</t>
-  </si>
-  <si>
-    <t>basketball | chess | wrestling | volleyball</t>
   </si>
   <si>
     <t>Not enough knowledge to judge confidently</t>
@@ -2585,47 +2585,47 @@
         <v>0.0</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J3" s="7"/>
       <c r="L3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" ht="48.0" customHeight="1">
       <c r="A4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="H4" s="8">
         <v>0.0</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="7"/>
       <c r="L4" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>56</v>
@@ -2753,7 +2753,7 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="7"/>
     </row>
@@ -2783,7 +2783,7 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J9" s="7"/>
     </row>
@@ -2813,7 +2813,7 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J10" s="7"/>
     </row>
@@ -2873,7 +2873,7 @@
         <v>1.0</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J12" s="7"/>
     </row>
@@ -2933,7 +2933,7 @@
         <v>0.0</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J14" s="7"/>
     </row>
@@ -2942,7 +2942,7 @@
         <v>119</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>120</v>
@@ -2963,7 +2963,7 @@
         <v>1.0</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J15" s="7"/>
     </row>
@@ -2993,7 +2993,7 @@
         <v>1.0</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J16" s="7"/>
     </row>
@@ -3002,7 +3002,7 @@
         <v>129</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>130</v>
@@ -3023,7 +3023,7 @@
         <v>1.0</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J17" s="7"/>
     </row>
@@ -3113,31 +3113,31 @@
         <v>0.0</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J20" s="7"/>
     </row>
     <row r="21" ht="48.0" customHeight="1">
       <c r="A21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>153</v>
       </c>
       <c r="F21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="H21" s="8">
         <v>1.0</v>
@@ -3173,7 +3173,7 @@
         <v>1.0</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J22" s="7"/>
     </row>
@@ -3233,7 +3233,7 @@
         <v>1.0</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J24" s="7"/>
     </row>
@@ -3242,7 +3242,7 @@
         <v>171</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>172</v>
@@ -3263,7 +3263,7 @@
         <v>0.0</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J25" s="7"/>
     </row>
@@ -3293,7 +3293,7 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J26" s="7"/>
     </row>
@@ -3323,7 +3323,7 @@
         <v>1.0</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J27" s="7"/>
     </row>
@@ -3332,7 +3332,7 @@
         <v>189</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>190</v>
@@ -3383,7 +3383,7 @@
         <v>0.0</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J29" s="7"/>
     </row>
@@ -3413,7 +3413,7 @@
         <v>0.0</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J30" s="7"/>
     </row>
@@ -3473,7 +3473,7 @@
         <v>0.0</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J32" s="7"/>
     </row>
@@ -3482,7 +3482,7 @@
         <v>218</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>219</v>
@@ -3491,7 +3491,7 @@
         <v>220</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>221</v>
@@ -3533,7 +3533,7 @@
         <v>0.0</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J34" s="7"/>
     </row>
@@ -3542,7 +3542,7 @@
         <v>228</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>229</v>
@@ -3551,7 +3551,7 @@
         <v>230</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>231</v>
@@ -3593,7 +3593,7 @@
         <v>1.0</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J36" s="7"/>
     </row>
@@ -3743,7 +3743,7 @@
         <v>0.0</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J41" s="7"/>
     </row>
@@ -3803,7 +3803,7 @@
         <v>1.0</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J43" s="7"/>
     </row>
@@ -3863,7 +3863,7 @@
         <v>0.0</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J45" s="7"/>
     </row>
@@ -3893,7 +3893,7 @@
         <v>1.0</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J46" s="7"/>
     </row>
@@ -3962,7 +3962,7 @@
         <v>301</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>302</v>
@@ -4013,7 +4013,7 @@
         <v>0.0</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J50" s="7"/>
     </row>
@@ -4022,7 +4022,7 @@
         <v>171</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>172</v>
@@ -4043,7 +4043,7 @@
         <v>0.0</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J51" s="7"/>
     </row>
